--- a/test/list/rajadesa/sirnabaya/list_sirnabaya_2.xlsx
+++ b/test/list/rajadesa/sirnabaya/list_sirnabaya_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\dds req\list\rajadesa\sirnabaya\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\rajadesa\sirnabaya\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154F96D5-4764-4059-807D-D125BE9B5080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB4D8A9-4FAA-4061-BF43-640292873A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="179">
   <si>
     <t>nama</t>
   </si>
@@ -112,484 +112,457 @@
     <t>014</t>
   </si>
   <si>
-    <t>Lampu jalan di depan rumah saya tidak menyala ketika malam.</t>
-  </si>
-  <si>
-    <t>Jalan di sekitar lingkungan kami berlubang dan perlu diperbaiki.</t>
-  </si>
-  <si>
-    <t>Sampah di taman umum tidak dibersihkan secara teratur.</t>
-  </si>
-  <si>
-    <t>Sistem drainase di daerah kami tidak berfungsi dengan baik saat hujan.</t>
-  </si>
-  <si>
-    <t>Ada kebisingan berlebihan dari pabrik yang mengganggu kenyamanan tinggal kami.</t>
-  </si>
-  <si>
-    <t>Fasilitas olahraga seperti lapangan sepak bola dan lapangan basket rusak dan tidak diperbaiki.</t>
-  </si>
-  <si>
-    <t>Tidak ada tempat penampungan sampah yang cukup di sekitar kami.</t>
-  </si>
-  <si>
-    <t>Air minum dari kran di rumah kami terasa kotor dan berbau.</t>
-  </si>
-  <si>
-    <t>Sekolah setempat kurang memadai dalam menyediakan fasilitas pendidikan yang memadai.</t>
-  </si>
-  <si>
-    <t>Gang-gang di lingkungan kami tidak terawat dan menjadi sarang nyamuk.</t>
-  </si>
-  <si>
-    <t>Perluasan jalan di sekitar kami menyebabkan kemacetan lalu lintas yang parah.</t>
-  </si>
-  <si>
-    <t>Kualitas udara di lingkungan kami buruk karena polusi kendaraan.</t>
-  </si>
-  <si>
-    <t>Rute angkutan umum ke daerah kami tidak memadai untuk masyarakat.</t>
-  </si>
-  <si>
-    <t>Listrik sering mati dan pemadaman berlangsung lama di lingkungan kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada fasilitas kesehatan yang memadai di dekat tempat tinggal kami.</t>
-  </si>
-  <si>
-    <t>Tingkat kejahatan di lingkungan kami meningkat dan perlu keamanan yang lebih baik.</t>
-  </si>
-  <si>
-    <t>Tidak ada tempat bermain untuk anak-anak di sekitar kami.</t>
-  </si>
-  <si>
-    <t>Kualitas air di sungai atau danau terdekat tercemar dan perlu diperbaiki.</t>
-  </si>
-  <si>
-    <t>Ruang publik seperti taman dan area hijau tidak dirawat dengan baik.</t>
-  </si>
-  <si>
-    <t>Kualitas penerangan di jalan-jalan kami buruk dan perlu ditingkatkan.</t>
-  </si>
-  <si>
-    <t>Kurangnya tempat parkir yang memadai di sekitar toko dan pusat perbelanjaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya lapangan kerja di lingkungan kami membuat ekonomi warga sulit.</t>
-  </si>
-  <si>
-    <t>Internet di daerah kami tidak stabil dan sering putus.</t>
-  </si>
-  <si>
-    <t>Tidak adanya aksesibilitas bagi orang dengan kebutuhan khusus di tempat umum.</t>
-  </si>
-  <si>
-    <t>Binatang liar seperti anjing liar menjadi masalah di lingkungan kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada jalur pejalan kaki yang aman di sekitar jalan-jalan utama.</t>
-  </si>
-  <si>
-    <t>Tidak adanya ruang terbuka hijau yang cukup di dekat tempat tinggal kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada layanan angkutan umum pada larut malam di wilayah kami.</t>
-  </si>
-  <si>
-    <t>Bangunan yang ditinggalkan dan tidak terawat di sekitar kami menjadi tempat tinggal bagi tikus dan serangga.</t>
-  </si>
-  <si>
-    <t>Kurangnya tempat ibadah yang memadai di daerah kami.</t>
-  </si>
-  <si>
-    <t>Kurangnya fasilitas belajar yang memadai di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Buku teks dan materi pembelajaran yang digunakan sudah usang dan tidak diperbarui.</t>
-  </si>
-  <si>
-    <t>Tingkat kualitas pengajaran guru di beberapa sekolah rendah.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pendidikan keterampilan hidup yang diajarkan di sekolah.</t>
-  </si>
-  <si>
-    <t>Overcrowding (kepadatan) di kelas-kelas sehingga siswa tidak mendapatkan perhatian yang cukup dari guru.</t>
-  </si>
-  <si>
-    <t>Kurangnya aksesibilitas untuk siswa dengan kebutuhan khusus di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Program kurikulum yang tidak relevan dengan kebutuhan dunia kerja.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan dan sumber daya untuk siswa yang berprestasi akademik.</t>
-  </si>
-  <si>
-    <t>Kurangnya kesempatan untuk terlibat dalam kegiatan ekstrakurikuler.</t>
-  </si>
-  <si>
-    <t>Kurangnya pelatihan dan pembinaan untuk guru baru yang masuk.</t>
-  </si>
-  <si>
-    <t>Kurangnya fasilitas laboratorium ilmiah dan komputer di sekolah kami.</t>
-  </si>
-  <si>
-    <t>Kualitas makanan di kantin sekolah kami tidak sehat dan tidak bergizi.</t>
-  </si>
-  <si>
-    <t>Banyak siswa yang melakukan pelecehan atau kekerasan di lingkungan sekolah.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan dan pemahaman bagi siswa dengan masalah kesehatan mental.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pengembangan keterampilan kepemimpinan dan kolaborasi di sekolah.</t>
-  </si>
-  <si>
-    <t>Banyaknya kegiatan pengajaran yang terlalu terfokus pada tes dan bukan pada pemahaman konsep.</t>
-  </si>
-  <si>
-    <t>Kurangnya perhatian terhadap seni dan musik di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program bantuan atau beasiswa bagi siswa yang kurang mampu secara finansial.</t>
-  </si>
-  <si>
-    <t>Kurangnya guru yang berkualitas dan terlatih di beberapa sekolah pedesaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya sarana transportasi bagi siswa yang tinggal di daerah terpencil.</t>
-  </si>
-  <si>
-    <t>Tingkat disiplin yang rendah di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Tidak adanya pendekatan individual dalam pembelajaran bagi siswa dengan kecepatan belajar yang berbeda.</t>
-  </si>
-  <si>
-    <t>Kurangnya kesempatan untuk berpartisipasi dalam pertukaran pelajar atau program internasional.</t>
-  </si>
-  <si>
-    <t>Kurangnya keterlibatan orang tua dalam pendidikan anak-anak mereka.</t>
-  </si>
-  <si>
-    <t>Tidak adanya konseling karir yang memadai untuk siswa-siswa kami.</t>
-  </si>
-  <si>
-    <t>Kurangnya penekanan pada pendidikan karakter dan etika di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Sistem penilaian yang tidak adil dan kurang transparan.</t>
-  </si>
-  <si>
-    <t>Kurangnya pembaruan teknologi pendidikan di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Banyaknya siswa yang putus sekolah atau tidak melanjutkan pendidikan ke jenjang yang lebih tinggi.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program vokasional yang memadai untuk siswa yang tidak melanjutkan ke perguruan tinggi.</t>
-  </si>
-  <si>
-    <t>Kurangnya sarana perpustakaan yang memadai di beberapa sekolah.</t>
-  </si>
-  <si>
-    <t>Kurangnya perhatian pada pendidikan inklusif untuk siswa dengan kebutuhan khusus.</t>
-  </si>
-  <si>
-    <t>Kurangnya pemahaman tentang pentingnya pendidikan seksual yang komprehensif.</t>
-  </si>
-  <si>
-    <t>Kurangnya pelatihan penggunaan teknologi bagi guru dan siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pendidikan tentang keberlanjutan dan lingkungan hidup.</t>
-  </si>
-  <si>
-    <t>Ketidakadilan dalam alokasi dana pendidikan antara daerah perkotaan dan pedesaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya transparansi dalam penggunaan dana pendidikan.</t>
-  </si>
-  <si>
-    <t>Kurangnya pembinaan keterampilan kewirausahaan bagi siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan untuk pendidikan seni dan budaya.</t>
-  </si>
-  <si>
-    <t>Tidak adanya akses internet yang memadai di sekolah-sekolah kami.</t>
-  </si>
-  <si>
     <t>Kurangnya penanganan kasus bullying dan kekerasan di sekolah secara tegas.</t>
   </si>
   <si>
     <t>Kurangnya kerjasama antara sekolah dan komunitas lokal.</t>
   </si>
   <si>
-    <t>Kurangnya program mentorship atau bimbingan akademik bagi siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya peluang untuk pengembangan kepemimpinan siswa dalam kegiatan sekolah.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program pendidikan tentang keuangan pribadi dan pengelolaan uang.</t>
-  </si>
-  <si>
-    <t>2023-07-11</t>
-  </si>
-  <si>
-    <t>2023-07-12</t>
-  </si>
-  <si>
-    <t>2023-07-13</t>
-  </si>
-  <si>
-    <t>2023-07-14</t>
-  </si>
-  <si>
-    <t>2023-07-15</t>
-  </si>
-  <si>
-    <t>2023-07-17</t>
-  </si>
-  <si>
-    <t>2023-07-18</t>
-  </si>
-  <si>
-    <t>2023-07-19</t>
-  </si>
-  <si>
-    <t>2023-07-20</t>
-  </si>
-  <si>
-    <t>2023-07-21</t>
-  </si>
-  <si>
-    <t>2023-07-22</t>
-  </si>
-  <si>
-    <t>2023-07-24</t>
-  </si>
-  <si>
-    <t>2023-07-25</t>
-  </si>
-  <si>
-    <t>SITI ROHMAH</t>
-  </si>
-  <si>
-    <t>EEM</t>
-  </si>
-  <si>
-    <t>YOYON MARYONO</t>
-  </si>
-  <si>
-    <t>AI YULIAWATI</t>
-  </si>
-  <si>
-    <t>HILQI HAIKAL ALAMSAH</t>
-  </si>
-  <si>
-    <t>MAHESA JIAN NANDANA</t>
-  </si>
-  <si>
-    <t>DIAH</t>
-  </si>
-  <si>
-    <t>DIDIN BASOLI ALWI</t>
-  </si>
-  <si>
-    <t>JUNTI</t>
-  </si>
-  <si>
-    <t>SITI</t>
-  </si>
-  <si>
-    <t>RUKANAH</t>
-  </si>
-  <si>
-    <t>MABRURI</t>
-  </si>
-  <si>
-    <t>MAYA SARI</t>
-  </si>
-  <si>
-    <t>ABDUL RAHMAN</t>
-  </si>
-  <si>
-    <t>ENDANG TRIYASIH</t>
-  </si>
-  <si>
-    <t>RISKA RAHMAYANTI</t>
-  </si>
-  <si>
-    <t>SUPRIADI</t>
-  </si>
-  <si>
     <t>NURHASANAH</t>
   </si>
   <si>
-    <t>RIANKA PUTRA RAMADHAN</t>
-  </si>
-  <si>
-    <t>SILVY AULIA NATASARI</t>
-  </si>
-  <si>
-    <t>MAMAN FATHUROHMAN</t>
-  </si>
-  <si>
-    <t>SITI MAPTUHAH</t>
-  </si>
-  <si>
-    <t>LISTIANY EVHEN JABAR</t>
-  </si>
-  <si>
-    <t>IIK RIDWAN ALIF  FIQRILLAH</t>
-  </si>
-  <si>
-    <t>MIRA MIRNAWATI</t>
-  </si>
-  <si>
-    <t>MUHAMMAD  AJIB NASRULLAH</t>
-  </si>
-  <si>
-    <t>AJAT SUDRAJAT</t>
-  </si>
-  <si>
-    <t>HERI</t>
-  </si>
-  <si>
-    <t>ELI SRI NOVIA EVIYANI</t>
-  </si>
-  <si>
-    <t>RASIWAN</t>
-  </si>
-  <si>
-    <t>JAENAH</t>
-  </si>
-  <si>
     <t>SULAEMAN</t>
   </si>
   <si>
-    <t>WAWAN RAHWAN</t>
-  </si>
-  <si>
-    <t>INING WARNENGSIH</t>
-  </si>
-  <si>
-    <t>ADE PIAN ASSAURI</t>
-  </si>
-  <si>
-    <t>ADE REZKY KHOERUL ANAM</t>
-  </si>
-  <si>
-    <t>MIS`AN</t>
-  </si>
-  <si>
-    <t>JAJANG NURJAMAN</t>
-  </si>
-  <si>
-    <t>RAENI NURAENI</t>
-  </si>
-  <si>
-    <t>MUHAMAD ZILDAN NUR FAISAL</t>
-  </si>
-  <si>
-    <t>YADI</t>
-  </si>
-  <si>
-    <t>ANWAR NASIHIN</t>
-  </si>
-  <si>
-    <t>IDA SITI HAMIDAH</t>
-  </si>
-  <si>
-    <t>MUHAMMAD AZMI ZAIDAN</t>
-  </si>
-  <si>
-    <t>ROKIM</t>
-  </si>
-  <si>
-    <t>NANI MARYANI</t>
-  </si>
-  <si>
-    <t>FARID FAJAR SIDIK</t>
-  </si>
-  <si>
-    <t>TEDI SETIADI</t>
-  </si>
-  <si>
-    <t>RINI ANDRIANI</t>
-  </si>
-  <si>
-    <t>NANDA AMMAR PRAMADANA</t>
-  </si>
-  <si>
-    <t>AHMAD SHAKA ARKAN WIRATAMA</t>
-  </si>
-  <si>
-    <t>MAMAH</t>
-  </si>
-  <si>
-    <t>YOYO FATHUROHMAN</t>
-  </si>
-  <si>
-    <t>NURUL PINI ALPIONITA</t>
-  </si>
-  <si>
-    <t>NAURA ADIVA AZAHRA</t>
-  </si>
-  <si>
-    <t>HASBULLOH</t>
-  </si>
-  <si>
-    <t>ANNISA OCHTAVIA</t>
-  </si>
-  <si>
-    <t>MIKHAYLA KEISHA RAFIFAH</t>
-  </si>
-  <si>
-    <t>UDIN</t>
-  </si>
-  <si>
-    <t>ILAH</t>
-  </si>
-  <si>
-    <t>SOLEH</t>
-  </si>
-  <si>
-    <t>KURTINI</t>
-  </si>
-  <si>
-    <t>SALMAN</t>
-  </si>
-  <si>
-    <t>LANI LISTRIANI</t>
-  </si>
-  <si>
-    <t>MUHAMAD FALQI TAJUZZAMAN</t>
-  </si>
-  <si>
-    <t>MUHAMAD IHSAN AMNUL BARIYAH</t>
-  </si>
-  <si>
-    <t>AGUS SALIM</t>
-  </si>
-  <si>
-    <t>SITI MARYAM</t>
-  </si>
-  <si>
     <t>ALFIAN MARDIANA</t>
   </si>
   <si>
-    <t>YAYAH QODARIAH</t>
-  </si>
-  <si>
-    <t>ANDIKA RAMADHAN</t>
-  </si>
-  <si>
-    <t>ADE DIAN MIFTAH AL FAUZI</t>
+    <t>Harga kebutuhan pokok terus meroket, sulit untuk mencukupi.</t>
+  </si>
+  <si>
+    <t>Pengangguran tinggi, sulit mencari pekerjaan yang layak.</t>
+  </si>
+  <si>
+    <t>Upah minimum belum cukup untuk memenuhi kebutuhan hidup.</t>
+  </si>
+  <si>
+    <t>Sulitnya akses kepada layanan kesehatan karena biaya yang tinggi.</t>
+  </si>
+  <si>
+    <t>Pendidikan berkualitas sulit dijangkau akibat biaya tinggi.</t>
+  </si>
+  <si>
+    <t>Besarnya beban pajak dan kurangnya manfaat yang dirasakan.</t>
+  </si>
+  <si>
+    <t>Harga sewa tempat tinggal terlalu tinggi di perkotaan.</t>
+  </si>
+  <si>
+    <t>Inflasi yang tidak terkendali menggerus daya beli.</t>
+  </si>
+  <si>
+    <t>Kesenjangan ekonomi antara kaya dan miskin semakin melebar.</t>
+  </si>
+  <si>
+    <t>Harga BBM dan energi terus naik, mengganggu mobilitas.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja di sektor industri kreatif.</t>
+  </si>
+  <si>
+    <t>Mahalnya biaya transportasi umum merugikan pekerja.</t>
+  </si>
+  <si>
+    <t>Sulitnya memenuhi kebutuhan pensiun di tengah kenaikan biaya hidup.</t>
+  </si>
+  <si>
+    <t>Rendahnya kualitas infrastruktur di beberapa daerah.</t>
+  </si>
+  <si>
+    <t>Hambatan birokrasi dan korupsi menghambat perkembangan usaha.</t>
+  </si>
+  <si>
+    <t>Investasi asing lebih diuntungkan daripada pengusaha lokal.</t>
+  </si>
+  <si>
+    <t>Sulitnya mendapatkan akses permodalan untuk startup.</t>
+  </si>
+  <si>
+    <t>Tingginya biaya produksi menghambat pertumbuhan industri.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses ke teknologi modern di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Sulitnya mengakses layanan keuangan seperti kredit usaha.</t>
+  </si>
+  <si>
+    <t>Kurangnya diversifikasi ekonomi mengandalkan sektor tertentu.</t>
+  </si>
+  <si>
+    <t>Harga properti yang tinggi sulit dijangkau generasi muda.</t>
+  </si>
+  <si>
+    <t>Mahalnya biaya komunikasi dan akses internet yang terbatas.</t>
+  </si>
+  <si>
+    <t>Sulitnya mengakses pasar ekspor bagi para pelaku usaha kecil.</t>
+  </si>
+  <si>
+    <t>Listrik sering mati, mengganggu aktivitas sehari-hari.</t>
+  </si>
+  <si>
+    <t>Transportasi umum tidak terjangkau dan tidak nyaman.</t>
+  </si>
+  <si>
+    <t>Fasilitas kesehatan minim, sulit mendapatkan perawatan.</t>
+  </si>
+  <si>
+    <t>Tempat sampah jarang disediakan, lingkungan kotor.</t>
+  </si>
+  <si>
+    <t>Kereta api sering terlambat, merugikan para penumpang.</t>
+  </si>
+  <si>
+    <t>Kualitas udara buruk karena minimnya pohon dan vegetasi.</t>
+  </si>
+  <si>
+    <t>Tidak ada sarana olahraga atau lapangan untuk warga.</t>
+  </si>
+  <si>
+    <t>Fasilitas perbelanjaan terbatas, harus pergi jauh untuk belanja.</t>
+  </si>
+  <si>
+    <t>Kerusakan infrastruktur menyulitkan petani dalam mengangkut hasil pertanian.</t>
+  </si>
+  <si>
+    <t>Kualitas jaringan telepon seluler buruk di beberapa area.</t>
+  </si>
+  <si>
+    <t>Minimnya jalur sepeda membuat sulit bagi pengendara sepeda.</t>
+  </si>
+  <si>
+    <t>Kelistrikan sering terganggu akibat cuaca ekstrem.</t>
+  </si>
+  <si>
+    <t>Pembangunan trotoar yang tidak merata dan berbahaya.</t>
+  </si>
+  <si>
+    <t>Tidak ada jalur khusus transportasi umum, menyebabkan kemacetan.</t>
+  </si>
+  <si>
+    <t>Pipa air tua sering bocor dan mengganggu pasokan air.</t>
+  </si>
+  <si>
+    <t>Keterbatasan aksesibilitas bagi penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan pendapatan dan kesenjangan sosial yang semakin lebar, menciptakan keresahan di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap layanan kesehatan berkualitas, membuat banyak orang kesulitan mendapatkan perawatan yang dibutuhkan.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja dan peluang ekonomi yang memadai, meningkatkan tingkat pengangguran dan ketidakpastian pekerjaan.</t>
+  </si>
+  <si>
+    <t>Sistem pendidikan yang tidak merata dan kurang berkualitas, menghambat kemajuan sosial dan ekonomi bagi sebagian masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>Sulitnya mendapatkan kredit untuk usaha kecil dan menengah.</t>
+  </si>
+  <si>
+    <t>Keterbatasan peluang ekonomi di daerah pedesaan menyulitkan warga.</t>
+  </si>
+  <si>
+    <t>Sulitnya akses modal untuk pertanian modern di desa.</t>
+  </si>
+  <si>
+    <t>Sistem perpajakan yang rumit dan membingungkan masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya dukungan untuk pelatihan keterampilan dari pemerintah terhadap masyarakat.</t>
+  </si>
+  <si>
+    <t>Krisis ekonomi membuat banyak usaha gulung tikar dan ekonomi sulit.</t>
+  </si>
+  <si>
+    <t>Jalan berlubang menyebabkan kerusakan kendaraan masyarakat.</t>
+  </si>
+  <si>
+    <t>Tidak ada akses air bersih di daerah kami menyulitkan warga.</t>
+  </si>
+  <si>
+    <t>Jembatan rusak menghambat mobilitas warga desa yang berlalu lalang.</t>
+  </si>
+  <si>
+    <t>Drainase buruk menyebabkan banjir saat hujan deras melanda.</t>
+  </si>
+  <si>
+    <t>Tidak ada akses internet di daerah pedesaan membuat warga kesulitan.</t>
+  </si>
+  <si>
+    <t>Sekolah dalam kondisi rusak, kurang memadai bagi masyarakat.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat rekreasi atau taman di sekitar desa.</t>
+  </si>
+  <si>
+    <t>Jalur pejalan kaki tidak aman untuk digunakan bagi warga.</t>
+  </si>
+  <si>
+    <t>Kurangnya lampu jalan membuat malam hari gelap dan rawan.</t>
+  </si>
+  <si>
+    <t>Keterbatasan tempat parkir di pusat desa kami sangat menyulitkan.</t>
+  </si>
+  <si>
+    <t>kendaraan umum yang sulit dijumpai di wilayah terpencil.</t>
+  </si>
+  <si>
+    <t>kondisi jalan yang kumuh dan tidak terawat rawan-.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat penampungan untuk hewan jalanan di jalan.</t>
+  </si>
+  <si>
+    <t>Minimnya tempat parkir untuk kendaraan umum di tempat kami.</t>
+  </si>
+  <si>
+    <t>PAJAR AL AJIS</t>
+  </si>
+  <si>
+    <t>TETI SEPTIANI</t>
+  </si>
+  <si>
+    <t>BAGAS</t>
+  </si>
+  <si>
+    <t>JANA</t>
+  </si>
+  <si>
+    <t>WATI</t>
+  </si>
+  <si>
+    <t>FAUZAN HAIKAL FIQRI</t>
+  </si>
+  <si>
+    <t>MARKUS</t>
+  </si>
+  <si>
+    <t>N ERUM</t>
+  </si>
+  <si>
+    <t>G. WATI DARWATI NURHIDAYAT</t>
+  </si>
+  <si>
+    <t>DODIH</t>
+  </si>
+  <si>
+    <t>ADILA AZZAHRA</t>
+  </si>
+  <si>
+    <t>SYIPA NURUL AULIA</t>
+  </si>
+  <si>
+    <t>JENI ARIPIN</t>
+  </si>
+  <si>
+    <t>IBROHIM</t>
+  </si>
+  <si>
+    <t>ODAH SITI SAODAH</t>
+  </si>
+  <si>
+    <t>ANSOR</t>
+  </si>
+  <si>
+    <t>NINING</t>
+  </si>
+  <si>
+    <t>MUHAMAD KODAR</t>
+  </si>
+  <si>
+    <t>TARSIDIN</t>
+  </si>
+  <si>
+    <t>ZAHROTUSITA</t>
+  </si>
+  <si>
+    <t>DASKIWA</t>
+  </si>
+  <si>
+    <t>AMINI</t>
+  </si>
+  <si>
+    <t>YAHYA</t>
+  </si>
+  <si>
+    <t>IKAH</t>
+  </si>
+  <si>
+    <t>NURYANAH</t>
+  </si>
+  <si>
+    <t>SAHRUR RAMDANI</t>
+  </si>
+  <si>
+    <t>ATONG DEDI</t>
+  </si>
+  <si>
+    <t>SOPIAH</t>
+  </si>
+  <si>
+    <t>RITA NUR AZIZAH</t>
+  </si>
+  <si>
+    <t>SUHARYO</t>
+  </si>
+  <si>
+    <t>KOLSUM</t>
+  </si>
+  <si>
+    <t>DARSA</t>
+  </si>
+  <si>
+    <t>TITIN</t>
+  </si>
+  <si>
+    <t>AMININ</t>
+  </si>
+  <si>
+    <t>TARCAH</t>
+  </si>
+  <si>
+    <t>TEDI SYAH</t>
+  </si>
+  <si>
+    <t>SOLEH YANTO</t>
+  </si>
+  <si>
+    <t>ENE SA'ADAH</t>
+  </si>
+  <si>
+    <t>KHANIF</t>
+  </si>
+  <si>
+    <t>SINTA AGUSTINA</t>
+  </si>
+  <si>
+    <t>TARMAN</t>
+  </si>
+  <si>
+    <t>DARHAM</t>
+  </si>
+  <si>
+    <t>SUKIRAH</t>
+  </si>
+  <si>
+    <t>WASNAMA</t>
+  </si>
+  <si>
+    <t>UPIN</t>
+  </si>
+  <si>
+    <t>TAUFIK HIDAYAT</t>
+  </si>
+  <si>
+    <t>TASLAM</t>
+  </si>
+  <si>
+    <t>ANAH</t>
+  </si>
+  <si>
+    <t>SITI ZAHRA ROMDONI</t>
+  </si>
+  <si>
+    <t>NURDIN</t>
+  </si>
+  <si>
+    <t>EROH</t>
+  </si>
+  <si>
+    <t>MUHAMAD FAZRI</t>
+  </si>
+  <si>
+    <t>TASIMI</t>
+  </si>
+  <si>
+    <t>AHWA</t>
+  </si>
+  <si>
+    <t>PATIMAH</t>
+  </si>
+  <si>
+    <t>EMPUD</t>
+  </si>
+  <si>
+    <t>SURYANI</t>
+  </si>
+  <si>
+    <t>HASAN NURUL IHSAN</t>
+  </si>
+  <si>
+    <t>NA'I SITI ROHMAH</t>
+  </si>
+  <si>
+    <t>NINA HERNIAWATI</t>
+  </si>
+  <si>
+    <t>KOMAR</t>
+  </si>
+  <si>
+    <t>ROHIILAH</t>
+  </si>
+  <si>
+    <t>ADE REHAN SAPUTRA</t>
+  </si>
+  <si>
+    <t>CINDI RAHMAWATI</t>
+  </si>
+  <si>
+    <t>DARKA</t>
+  </si>
+  <si>
+    <t>ELAH</t>
+  </si>
+  <si>
+    <t>JENAL ASIKIN</t>
+  </si>
+  <si>
+    <t>SIFA NOVIA NUR AZIZAH</t>
+  </si>
+  <si>
+    <t>2023-08-15</t>
+  </si>
+  <si>
+    <t>2023-08-16</t>
+  </si>
+  <si>
+    <t>2023-08-17</t>
+  </si>
+  <si>
+    <t>2023-08-18</t>
+  </si>
+  <si>
+    <t>2023-08-19</t>
+  </si>
+  <si>
+    <t>2023-08-21</t>
+  </si>
+  <si>
+    <t>2023-08-22</t>
+  </si>
+  <si>
+    <t>2023-08-23</t>
   </si>
 </sst>
 </file>
@@ -1012,29 +985,29 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Cigoong</v>
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>004</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>008</v>
       </c>
       <c r="G2" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1042,29 +1015,29 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubang</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>003</v>
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>006</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1072,10 +1045,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1083,18 +1056,18 @@
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>006</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>003</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1102,29 +1075,29 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>015</v>
       </c>
       <c r="G5" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1132,29 +1105,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>014</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>014</v>
       </c>
       <c r="G6" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1162,29 +1135,29 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Cigoong</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>001</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>007</v>
       </c>
       <c r="G7" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1192,18 +1165,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>002</v>
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1214,7 +1187,7 @@
         <v>Sirnabaya</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1222,29 +1195,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>012</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>004</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1252,29 +1225,29 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubang</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>007</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>006</v>
       </c>
       <c r="G10" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1282,29 +1255,29 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>015</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>002</v>
       </c>
       <c r="G11" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1312,29 +1285,29 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>002</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>010</v>
       </c>
       <c r="G12" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1342,10 +1315,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1353,18 +1326,18 @@
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>003</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="G13" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1372,10 +1345,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1383,18 +1356,18 @@
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>005</v>
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>010</v>
       </c>
       <c r="G14" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1402,29 +1375,29 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kutasari</v>
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>005</v>
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>008</v>
       </c>
       <c r="G15" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1432,29 +1405,29 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>008</v>
       </c>
       <c r="G16" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1462,29 +1435,29 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kutasari</v>
       </c>
       <c r="E17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>001</v>
       </c>
       <c r="F17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>004</v>
       </c>
       <c r="G17" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1492,29 +1465,29 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>001</v>
       </c>
       <c r="F18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>007</v>
       </c>
       <c r="G18" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -1522,29 +1495,29 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>013</v>
       </c>
       <c r="F19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>010</v>
       </c>
       <c r="G19" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -1552,29 +1525,29 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>006</v>
       </c>
       <c r="F20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>002</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -1582,10 +1555,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1593,18 +1566,18 @@
       </c>
       <c r="E21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>015</v>
       </c>
       <c r="F21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>011</v>
       </c>
       <c r="G21" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -1612,29 +1585,29 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>008</v>
       </c>
-      <c r="F22" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
-      </c>
       <c r="G22" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -1642,29 +1615,29 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>003</v>
       </c>
       <c r="F23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>001</v>
       </c>
       <c r="G23" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -1672,29 +1645,29 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>014</v>
       </c>
       <c r="F24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>007</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -1702,29 +1675,29 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="D25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubang</v>
       </c>
       <c r="E25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>009</v>
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>001</v>
       </c>
       <c r="G25" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H25" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -1732,22 +1705,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>003</v>
       </c>
       <c r="F26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>009</v>
       </c>
       <c r="G26" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1762,10 +1735,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="D27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1773,18 +1746,18 @@
       </c>
       <c r="E27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="F27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="G27" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H27" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -1792,10 +1765,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1803,18 +1776,18 @@
       </c>
       <c r="E28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>015</v>
       </c>
       <c r="F28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>002</v>
       </c>
       <c r="G28" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -1822,29 +1795,29 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubang</v>
       </c>
       <c r="E29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>015</v>
       </c>
       <c r="F29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>002</v>
       </c>
       <c r="G29" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -1852,10 +1825,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1863,18 +1836,18 @@
       </c>
       <c r="E30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>004</v>
       </c>
       <c r="F30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>004</v>
       </c>
       <c r="G30" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -1882,18 +1855,18 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubang</v>
       </c>
       <c r="E31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>009</v>
       </c>
       <c r="F31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1904,7 +1877,7 @@
         <v>Sirnabaya</v>
       </c>
       <c r="H31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -1912,29 +1885,29 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>013</v>
       </c>
       <c r="F32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>012</v>
       </c>
       <c r="G32" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -1942,14 +1915,14 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="D33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Cigoong</v>
       </c>
       <c r="E33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1957,14 +1930,14 @@
       </c>
       <c r="F33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>012</v>
       </c>
       <c r="G33" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H33" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -1972,14 +1945,14 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1987,14 +1960,14 @@
       </c>
       <c r="F34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>006</v>
       </c>
       <c r="G34" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>60</v>
+      <c r="H34" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -2002,29 +1975,29 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kutasari</v>
       </c>
       <c r="E35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>009</v>
       </c>
       <c r="F35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>006</v>
       </c>
       <c r="G35" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>61</v>
+      <c r="H35" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -2032,29 +2005,29 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>015</v>
       </c>
       <c r="F36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>013</v>
       </c>
       <c r="G36" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>62</v>
+      <c r="H36" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -2062,29 +2035,29 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="F37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>014</v>
       </c>
       <c r="G37" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>63</v>
+      <c r="H37" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -2092,29 +2065,29 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="F38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>001</v>
       </c>
       <c r="G38" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>64</v>
+      <c r="H38" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -2122,29 +2095,29 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubang</v>
       </c>
       <c r="E39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>008</v>
       </c>
       <c r="F39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G39" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>65</v>
+      <c r="H39" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -2152,29 +2125,29 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>008</v>
       </c>
       <c r="F40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>012</v>
       </c>
       <c r="G40" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>66</v>
+      <c r="H40" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -2182,29 +2155,29 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="D41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kutasari</v>
       </c>
       <c r="E41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>004</v>
       </c>
       <c r="F41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>006</v>
       </c>
       <c r="G41" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>67</v>
+      <c r="H41" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -2212,29 +2185,29 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="D42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>007</v>
       </c>
       <c r="F42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>005</v>
       </c>
       <c r="G42" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H42" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -2242,29 +2215,29 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>013</v>
       </c>
       <c r="F43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>010</v>
       </c>
       <c r="G43" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>69</v>
+      <c r="H43" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -2272,10 +2245,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2283,18 +2256,18 @@
       </c>
       <c r="E44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>013</v>
       </c>
       <c r="F44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="G44" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>70</v>
+      <c r="H44" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -2302,29 +2275,29 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>003</v>
       </c>
       <c r="F45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>004</v>
       </c>
       <c r="G45" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>71</v>
+      <c r="H45" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -2332,29 +2305,29 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kutasari</v>
       </c>
       <c r="E46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>012</v>
       </c>
       <c r="F46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>001</v>
       </c>
       <c r="G46" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>72</v>
+      <c r="H46" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -2362,29 +2335,29 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubang</v>
       </c>
       <c r="E47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>007</v>
       </c>
       <c r="F47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>003</v>
       </c>
       <c r="G47" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>73</v>
+      <c r="H47" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -2392,29 +2365,29 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Cigoong</v>
       </c>
       <c r="E48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>007</v>
       </c>
-      <c r="F48" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
-      </c>
       <c r="G48" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>74</v>
+      <c r="H48" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -2422,29 +2395,29 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="D49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubang</v>
       </c>
       <c r="E49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>006</v>
       </c>
       <c r="F49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>008</v>
       </c>
       <c r="G49" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>75</v>
+      <c r="H49" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -2452,18 +2425,18 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>012</v>
       </c>
       <c r="F50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2473,8 +2446,8 @@
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>76</v>
+      <c r="H50" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -2482,10 +2455,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2493,18 +2466,18 @@
       </c>
       <c r="E51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="F51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>003</v>
       </c>
       <c r="G51" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H51" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -2512,10 +2485,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="D52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2523,18 +2496,18 @@
       </c>
       <c r="E52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="F52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>006</v>
       </c>
       <c r="G52" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>78</v>
+      <c r="H52" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -2542,29 +2515,29 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kutasari</v>
       </c>
       <c r="E53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>014</v>
       </c>
       <c r="F53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>010</v>
       </c>
       <c r="G53" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H53" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -2572,29 +2545,29 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="D54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kutasari</v>
       </c>
       <c r="E54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>003</v>
       </c>
       <c r="F54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>002</v>
       </c>
       <c r="G54" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H54" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -2602,29 +2575,29 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="D55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Kutasari</v>
       </c>
       <c r="E55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>007</v>
       </c>
       <c r="F55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>001</v>
       </c>
       <c r="G55" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H55" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -2632,29 +2605,29 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>007</v>
       </c>
       <c r="F56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>010</v>
       </c>
       <c r="G56" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H56" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -2662,10 +2635,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2673,18 +2646,18 @@
       </c>
       <c r="E57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>015</v>
       </c>
       <c r="F57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>012</v>
       </c>
       <c r="G57" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H57" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -2692,29 +2665,29 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubang</v>
       </c>
       <c r="E58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="F58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>012</v>
       </c>
       <c r="G58" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H58" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
@@ -2722,10 +2695,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2733,18 +2706,18 @@
       </c>
       <c r="E59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F59" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>001</v>
       </c>
-      <c r="F59" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
-      </c>
       <c r="G59" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H59" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
@@ -2752,29 +2725,29 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubang</v>
       </c>
       <c r="E60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>009</v>
       </c>
       <c r="F60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>012</v>
       </c>
       <c r="G60" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H60" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
@@ -2782,29 +2755,29 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Cigoong</v>
       </c>
       <c r="E61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>012</v>
       </c>
       <c r="F61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>005</v>
       </c>
       <c r="G61" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H61" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
@@ -2812,14 +2785,14 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -2827,14 +2800,14 @@
       </c>
       <c r="F62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>014</v>
       </c>
       <c r="G62" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H62" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -2842,29 +2815,29 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="D63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>010</v>
       </c>
       <c r="F63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>006</v>
       </c>
       <c r="G63" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H63" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
@@ -2872,29 +2845,29 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>015</v>
       </c>
       <c r="F64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>007</v>
       </c>
       <c r="G64" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H64" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
@@ -2902,29 +2875,29 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kubang</v>
       </c>
       <c r="E65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>010</v>
       </c>
       <c r="F65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>006</v>
       </c>
       <c r="G65" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H65" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
@@ -2932,10 +2905,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2943,18 +2916,18 @@
       </c>
       <c r="E66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>001</v>
       </c>
       <c r="F66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>010</v>
       </c>
       <c r="G66" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H66" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -2962,29 +2935,29 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kubang</v>
       </c>
       <c r="E67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>007</v>
       </c>
       <c r="F67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>008</v>
       </c>
       <c r="G67" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H67" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
@@ -2992,10 +2965,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -3003,18 +2976,18 @@
       </c>
       <c r="E68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>001</v>
       </c>
       <c r="F68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>007</v>
       </c>
       <c r="G68" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H68" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
@@ -3022,29 +2995,29 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="F69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="G69" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H69" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
@@ -3052,29 +3025,29 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="D70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="F70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>013</v>
       </c>
       <c r="G70" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H70" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
@@ -3082,29 +3055,29 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubang</v>
       </c>
       <c r="E71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>011</v>
       </c>
       <c r="F71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>002</v>
       </c>
       <c r="G71" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H71" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
@@ -3112,29 +3085,29 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="D72" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
+        <v>Cigoong</v>
       </c>
       <c r="E72" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>005</v>
       </c>
       <c r="F72" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>001</v>
       </c>
       <c r="G72" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H72" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
@@ -3142,120 +3115,51 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="D73" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E73" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>012</v>
       </c>
       <c r="F73" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="G73" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H73" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
-      </c>
-      <c r="F74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
-      </c>
-      <c r="G74" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Sirnabaya</v>
-      </c>
-      <c r="H74" t="s">
-        <v>100</v>
-      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="4"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
-      </c>
-      <c r="F75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
-      </c>
-      <c r="G75" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Sirnabaya</v>
-      </c>
-      <c r="H75" t="s">
-        <v>101</v>
-      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="4"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
-      </c>
-      <c r="F76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
-      </c>
-      <c r="G76" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Sirnabaya</v>
-      </c>
-      <c r="H76" t="s">
-        <v>102</v>
-      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="4"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C77" s="2"/>

--- a/test/list/rajadesa/sirnabaya/list_sirnabaya_2.xlsx
+++ b/test/list/rajadesa/sirnabaya/list_sirnabaya_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\rajadesa\sirnabaya\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB943E5-23C7-4D97-B427-D47A8889F8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BC358C-9CEB-4ADC-92D0-559629F19C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -16,17 +16,28 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="conf" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="145">
   <si>
     <t>nama</t>
   </si>
@@ -160,64 +171,307 @@
     <t>Minimnya tempat parkir untuk kendaraan umum di tempat kami.</t>
   </si>
   <si>
-    <t>ANAH</t>
-  </si>
-  <si>
-    <t>AHMAD</t>
-  </si>
-  <si>
-    <t>ENUR</t>
-  </si>
-  <si>
-    <t>WAFA NUR ADILLAH</t>
-  </si>
-  <si>
-    <t>RIZKY NUR HIDAYAT</t>
-  </si>
-  <si>
-    <t>KUSDI</t>
-  </si>
-  <si>
-    <t>TATANG</t>
-  </si>
-  <si>
-    <t>HERNAWATI</t>
-  </si>
-  <si>
-    <t>SAILA ALIKA PUTRI</t>
-  </si>
-  <si>
-    <t>ADIT RIANA</t>
-  </si>
-  <si>
-    <t>SALMAH</t>
-  </si>
-  <si>
-    <t>AGUN SRI GUNAWAN</t>
-  </si>
-  <si>
-    <t>KOKOM KOMALASARI</t>
-  </si>
-  <si>
-    <t>REVILANI NAZIRA GUNAWAN</t>
-  </si>
-  <si>
-    <t>REVALINA FARISA GUNAWAN</t>
-  </si>
-  <si>
-    <t>RAISHA FELICIA GUNAWAN</t>
-  </si>
-  <si>
-    <t>2023-09-05</t>
-  </si>
-  <si>
-    <t>2023-09-06</t>
-  </si>
-  <si>
-    <t>2023-09-07</t>
-  </si>
-  <si>
-    <t>2023-09-08</t>
+    <t>2023-10-10</t>
+  </si>
+  <si>
+    <t>2023-10-11</t>
+  </si>
+  <si>
+    <t>2023-10-12</t>
+  </si>
+  <si>
+    <t>2023-10-13</t>
+  </si>
+  <si>
+    <t>2023-10-14</t>
+  </si>
+  <si>
+    <t>2023-10-16</t>
+  </si>
+  <si>
+    <t>2023-10-17</t>
+  </si>
+  <si>
+    <t>2023-10-18</t>
+  </si>
+  <si>
+    <t>2023-10-19</t>
+  </si>
+  <si>
+    <t>2023-10-20</t>
+  </si>
+  <si>
+    <t>2023-10-21</t>
+  </si>
+  <si>
+    <t>2023-10-23</t>
+  </si>
+  <si>
+    <t>2023-10-24</t>
+  </si>
+  <si>
+    <t>Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>menurut $nama Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>Harga kebutuhan pokok naik terus, sulit untuk mencukupi kebutuhan sehari-hari.</t>
+  </si>
+  <si>
+    <t>Pekerjaan sulit dicari, pengangguran meningkat di wilayah ini.</t>
+  </si>
+  <si>
+    <t>Biaya pendidikan mahal, sulit bagi keluarga kurang mampu.</t>
+  </si>
+  <si>
+    <t>Persaingan usaha tidak sehat, usaha kecil sulit bertahan.</t>
+  </si>
+  <si>
+    <t>Banyak produk palsu, merugikan konsumen dan produsen asli.</t>
+  </si>
+  <si>
+    <t>Upah minimum rendah, sulit untuk hidup layak bagi warga.</t>
+  </si>
+  <si>
+    <t>Birokrasi perizinan usaha sulit dan memakan waktu.</t>
+  </si>
+  <si>
+    <t>Ketimpangan sosial dan ekonomi semakin besar, kesenjangan kaya-miskin.</t>
+  </si>
+  <si>
+    <t>Jalan rusak parah, mengganggu kelancaran lalu lintas dan merusak kendaraan.</t>
+  </si>
+  <si>
+    <t>Kemacetan lalu lintas yang parah, menyebabkan waktu tempuh yang lama.</t>
+  </si>
+  <si>
+    <t>Kurangnya perawatan rutin, membuat jalan semakin buruk.</t>
+  </si>
+  <si>
+    <t>Kurangnya penyeberangan pejalan kaki dan fasilitas untuk penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Kebutuhan perluasan jalan tidak terpenuhi, menyebabkan kemacetan terus bertambah.</t>
+  </si>
+  <si>
+    <t>Kurangnya penerangan jalan yang memadai, meningkatkan risiko kecelakaan di malam hari.</t>
+  </si>
+  <si>
+    <t>Jalan berlubang yang berbahaya bagi pengendara sepeda motor dan pengguna jalan lainnya.</t>
+  </si>
+  <si>
+    <t>Kurangnya trotoar yang aman, mengancam keselamatan pejalan kaki.</t>
+  </si>
+  <si>
+    <t>Parkir liar yang menghalangi akses jalan dan mengurangi ruang untuk kendaraan.</t>
+  </si>
+  <si>
+    <t>Kurangnya rambu lalu lintas yang jelas dan terawat, membingungkan pengguna jalan.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jalur sepeda yang aman, menghambat pengembangan transportasi berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Kendaraan parkir sembarangan di jalan, menyebabkan kemacetan dan kekacauan.</t>
+  </si>
+  <si>
+    <t>Jalan tidak terlayani saat hujan, menyebabkan banjir dan genangan air.</t>
+  </si>
+  <si>
+    <t>Tidak adanya fasilitas penyeberangan untuk hewan di jalan raya.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>Jalan tidak ramah lingkungan, tanpa pohon atau taman penyerap polusi.</t>
+  </si>
+  <si>
+    <t>Marka jalan yang pudar atau tidak terlihat jelas, meningkatkan risiko kecelakaan.</t>
+  </si>
+  <si>
+    <t>Kurangnya jalan alternatif untuk mengurangi kepadatan lalu lintas di ruas jalan utama.</t>
+  </si>
+  <si>
+    <t>KUSTIAWAN</t>
+  </si>
+  <si>
+    <t>UMU KULSUM</t>
+  </si>
+  <si>
+    <t>KAILA ZAHROTUN NISA</t>
+  </si>
+  <si>
+    <t>REVI AHMAD MAULIDAN</t>
+  </si>
+  <si>
+    <t>LISDIANA KUSTIAWATI</t>
+  </si>
+  <si>
+    <t>RUNTISAH</t>
+  </si>
+  <si>
+    <t>ALI</t>
+  </si>
+  <si>
+    <t>ASEP HAERUL MUSTOFA</t>
+  </si>
+  <si>
+    <t>CARTI</t>
+  </si>
+  <si>
+    <t>ISHAK</t>
+  </si>
+  <si>
+    <t>MUNAWAROH</t>
+  </si>
+  <si>
+    <t>KURNIA ADITYA RIZKY</t>
+  </si>
+  <si>
+    <t>HILMI ZAINI RAHIM</t>
+  </si>
+  <si>
+    <t>HILMAN ZAINI RAHMAN</t>
+  </si>
+  <si>
+    <t>YUSUF ABDUL MUIZ</t>
+  </si>
+  <si>
+    <t>DARMAD</t>
+  </si>
+  <si>
+    <t>JARIAH</t>
+  </si>
+  <si>
+    <t>APIP PERMANA</t>
+  </si>
+  <si>
+    <t>AI NURHANIDAH</t>
+  </si>
+  <si>
+    <t>IJA</t>
+  </si>
+  <si>
+    <t>YAYAH</t>
+  </si>
+  <si>
+    <t>ZAZA IJMA FAUZI</t>
+  </si>
+  <si>
+    <t>JUNED</t>
+  </si>
+  <si>
+    <t>TITI</t>
+  </si>
+  <si>
+    <t>OMAN</t>
+  </si>
+  <si>
+    <t>ROHANAH</t>
+  </si>
+  <si>
+    <t>DIOH</t>
+  </si>
+  <si>
+    <t>NANA SUTISNA</t>
+  </si>
+  <si>
+    <t>MIMIN</t>
+  </si>
+  <si>
+    <t>LILIS KURNIASARI</t>
+  </si>
+  <si>
+    <t>MINA ALFIYATUN NISA</t>
+  </si>
+  <si>
+    <t>AGUS</t>
+  </si>
+  <si>
+    <t>ADE CUCUM</t>
+  </si>
+  <si>
+    <t>DASEP JAMILUDIN</t>
+  </si>
+  <si>
+    <t>SOLEH</t>
+  </si>
+  <si>
+    <t>TATIN</t>
+  </si>
+  <si>
+    <t>SAIDAH ROBIATUS SOLIHAH</t>
+  </si>
+  <si>
+    <t>DIMAS</t>
+  </si>
+  <si>
+    <t>NOVI</t>
+  </si>
+  <si>
+    <t>MELI AGUSTIN</t>
+  </si>
+  <si>
+    <t>ARDI</t>
+  </si>
+  <si>
+    <t>EEN</t>
+  </si>
+  <si>
+    <t>NURPUDIN</t>
+  </si>
+  <si>
+    <t>DESI SRI RAHMAWATI</t>
+  </si>
+  <si>
+    <t>MUHAMAD RIDWAN</t>
+  </si>
+  <si>
+    <t>SYA'BANI JULIANA</t>
+  </si>
+  <si>
+    <t>KOKO</t>
+  </si>
+  <si>
+    <t>DANTIMI</t>
+  </si>
+  <si>
+    <t>ISAK</t>
+  </si>
+  <si>
+    <t>ROHIMAH</t>
+  </si>
+  <si>
+    <t>REVA AHMAD HIDAYAT</t>
+  </si>
+  <si>
+    <t>PIPIN RIFKI MAULANA</t>
+  </si>
+  <si>
+    <t>UJANG MUTOLIB</t>
+  </si>
+  <si>
+    <t>SITI ROHIMAH</t>
+  </si>
+  <si>
+    <t>FAHRI RAMDANI</t>
+  </si>
+  <si>
+    <t>ADIF ABDILAH</t>
   </si>
 </sst>
 </file>
@@ -225,7 +479,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -274,16 +528,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Mata Uang" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -300,7 +557,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -596,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330EDF8F-AF7E-4CFD-AD2A-76F45302569C}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
@@ -637,29 +894,29 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>010</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>012</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -667,29 +924,29 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>001</v>
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>011</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -697,14 +954,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -712,14 +969,14 @@
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>011</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H4" t="s">
-        <v>29</v>
+      <c r="H4" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -727,29 +984,29 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubang</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
-      </c>
-      <c r="G5" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v>Sirnabaya</v>
-      </c>
-      <c r="H5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -757,29 +1014,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
-      </c>
-      <c r="G6" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v>Sirnabaya</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -787,29 +1044,29 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kubang</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>012</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>010</v>
       </c>
       <c r="G7" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H7" t="s">
-        <v>31</v>
+      <c r="H7" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -817,29 +1074,29 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>015</v>
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>013</v>
       </c>
       <c r="G8" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H8" t="s">
-        <v>32</v>
+      <c r="H8" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -847,29 +1104,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>006</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>015</v>
       </c>
       <c r="G9" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H9" t="s">
-        <v>42</v>
+      <c r="H9" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -877,10 +1134,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -888,18 +1145,18 @@
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>008</v>
       </c>
       <c r="G10" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H10" t="s">
-        <v>33</v>
+      <c r="H10" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -907,29 +1164,29 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cigoong</v>
+        <v>Kutasari</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>014</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>001</v>
       </c>
       <c r="G11" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H11" t="s">
-        <v>34</v>
+      <c r="H11" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -937,29 +1194,29 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubang</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>013</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>012</v>
       </c>
       <c r="G12" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -967,10 +1224,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -978,18 +1235,18 @@
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>004</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>004</v>
       </c>
       <c r="G13" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H13" t="s">
-        <v>35</v>
+      <c r="H13" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -997,14 +1254,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kubangsari</v>
+        <v>Kutasari</v>
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1012,14 +1269,14 @@
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="G14" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H14" t="s">
-        <v>36</v>
+      <c r="H14" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1027,14 +1284,14 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Cigoong</v>
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1042,14 +1299,14 @@
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>002</v>
       </c>
       <c r="G15" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H15" t="s">
-        <v>37</v>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1057,29 +1314,29 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Kutasari</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>008</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>007</v>
       </c>
       <c r="G16" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Sirnabaya</v>
       </c>
-      <c r="H16" t="s">
-        <v>38</v>
+      <c r="H16" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1087,144 +1344,1110 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
         <v>Cigoong</v>
       </c>
-      <c r="E17" s="2" t="str">
+      <c r="E22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
         <v>001</v>
       </c>
-      <c r="F17" s="2" t="str">
+      <c r="F28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>012</v>
       </c>
-      <c r="G17" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v>Sirnabaya</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="G29" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G37" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G38" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G39" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G40" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G41" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H41" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C51" s="2"/>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G42" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G43" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H43" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G44" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G45" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G46" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G47" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G48" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G49" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H49" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G50" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H50" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G51" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H51" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G52" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G53" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G54" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H54" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kutasari</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G55" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cigoong</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G56" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Kubang</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G57" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Sirnabaya</v>
+      </c>
+      <c r="H57" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
